--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N24_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.261282109990394</v>
+        <v>1.017458342873439</v>
       </c>
       <c r="D2" t="n">
-        <v>4.600152514452724</v>
+        <v>0.7475247835985676</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
